--- a/data/Can Transitions 10_15.xlsx
+++ b/data/Can Transitions 10_15.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sahan\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alamancefoods-my.sharepoint.com/personal/balapradeepkonda_alamancefoods_com/Documents/Documents/GitHub/Bala_Can_SupplyChain/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02785BA2-3DA9-48D1-89E2-BC97967C355D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{02785BA2-3DA9-48D1-89E2-BC97967C355D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F2CA606-0A8F-4FAE-8694-3C5187B3F942}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{691FB9E4-0905-4364-99F9-B696A478F86B}"/>
+    <workbookView xWindow="11244" yWindow="-17472" windowWidth="30936" windowHeight="16776" xr2:uid="{691FB9E4-0905-4364-99F9-B696A478F86B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="42">
   <si>
     <t>ITEM DESCRIPTION</t>
   </si>
@@ -159,6 +159,15 @@
   </si>
   <si>
     <t>PK-A-CAN NON-DAIRY 15OZ CLASS</t>
+  </si>
+  <si>
+    <t>AM7 </t>
+  </si>
+  <si>
+    <t>PK-A-CAN 7OZ OAT WHIP TOPPING </t>
+  </si>
+  <si>
+    <t>Lard cut Transistion</t>
   </si>
 </sst>
 </file>
@@ -351,29 +360,29 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -709,20 +718,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3192465-F364-4878-96B2-165F606027ED}">
-  <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="3" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>31</v>
       </c>
@@ -747,12 +756,12 @@
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="I1" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="21"/>
-    </row>
-    <row r="2" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J1" s="17"/>
+    </row>
+    <row r="2" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>9</v>
       </c>
@@ -775,12 +784,12 @@
       <c r="H2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" s="17"/>
-    </row>
-    <row r="3" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I2" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="15"/>
+    </row>
+    <row r="3" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>11</v>
       </c>
@@ -803,12 +812,12 @@
       <c r="H3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="J3" s="17"/>
-    </row>
-    <row r="4" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I3" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="15"/>
+    </row>
+    <row r="4" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>13</v>
       </c>
@@ -831,12 +840,12 @@
       <c r="H4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="J4" s="17"/>
-    </row>
-    <row r="5" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I4" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="15"/>
+    </row>
+    <row r="5" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>15</v>
       </c>
@@ -859,12 +868,12 @@
       <c r="H5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="J5" s="17"/>
-    </row>
-    <row r="6" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I5" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="15"/>
+    </row>
+    <row r="6" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>17</v>
       </c>
@@ -887,12 +896,12 @@
       <c r="H6" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" s="17"/>
-    </row>
-    <row r="7" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I6" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="15"/>
+    </row>
+    <row r="7" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>19</v>
       </c>
@@ -915,12 +924,12 @@
       <c r="H7" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="I7" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7" s="17"/>
-    </row>
-    <row r="8" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I7" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" s="15"/>
+    </row>
+    <row r="8" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>21</v>
       </c>
@@ -943,12 +952,12 @@
       <c r="H8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I8" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="J8" s="17"/>
-    </row>
-    <row r="9" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I8" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="J8" s="15"/>
+    </row>
+    <row r="9" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>23</v>
       </c>
@@ -971,12 +980,12 @@
       <c r="H9" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="I9" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="J9" s="17"/>
-    </row>
-    <row r="10" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I9" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" s="15"/>
+    </row>
+    <row r="10" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>25</v>
       </c>
@@ -999,12 +1008,12 @@
       <c r="H10" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="I10" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="J10" s="17"/>
-    </row>
-    <row r="11" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I10" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="J10" s="15"/>
+    </row>
+    <row r="11" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>27</v>
       </c>
@@ -1027,12 +1036,12 @@
       <c r="H11" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="I11" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="J11" s="19"/>
-    </row>
-    <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="I11" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="J11" s="21"/>
+    </row>
+    <row r="12" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
         <v>33</v>
       </c>
@@ -1055,12 +1064,12 @@
       <c r="H12" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="I12" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="J12" s="15"/>
-    </row>
-    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="I12" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="J12" s="19"/>
+    </row>
+    <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
         <v>34</v>
       </c>
@@ -1083,12 +1092,12 @@
       <c r="H13" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="I13" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="J13" s="15"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I13" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="J13" s="19"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>37</v>
       </c>
@@ -1110,21 +1119,45 @@
       <c r="H14" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="I14" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="J14" s="15"/>
+      <c r="I14" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="J14" s="19"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="7"/>
+      <c r="C15" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="7">
+        <v>12867</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="7">
+        <v>12902</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I15" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="J15" s="21"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J14" xr:uid="{F3192465-F364-4878-96B2-165F606027ED}">
     <filterColumn colId="8" showButton="0"/>
   </autoFilter>
-  <mergeCells count="14">
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I3:J3"/>
+  <mergeCells count="15">
+    <mergeCell ref="I15:J15"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="I14:J14"/>
@@ -1134,6 +1167,11 @@
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I3:J3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
